--- a/Result/profitability/3593.xlsx
+++ b/Result/profitability/3593.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.31</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2725</v>
+        <v>-0.25625</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.359999999999983</v>
+        <v>-0.5337499999999826</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.83</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05874999999999998</v>
+        <v>-0.02499999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>2.728750000000018</v>
+        <v>2.756250000000018</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.77</v>
       </c>
       <c r="M4" t="n">
-        <v>0.165</v>
+        <v>0.12875</v>
       </c>
       <c r="N4" t="n">
-        <v>6.027500000000018</v>
+        <v>5.492500000000017</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.23375</v>
+        <v>0.17625</v>
       </c>
       <c r="N5" t="n">
-        <v>7.758750000000018</v>
+        <v>6.385000000000018</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0.315</v>
+        <v>0.2887500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>9.805000000000017</v>
+        <v>8.542500000000018</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.52</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4475</v>
+        <v>0.3037500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>12.17625000000002</v>
+        <v>11.84875000000002</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.79</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6212500000000001</v>
+        <v>0.615</v>
       </c>
       <c r="N8" t="n">
-        <v>15.94875000000002</v>
+        <v>16.37375000000002</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.35</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7025</v>
+        <v>0.7024999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>19.83875000000002</v>
@@ -1772,7 +1772,7 @@
         <v>0.23</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6275000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>19.45625000000002</v>
@@ -1899,7 +1899,7 @@
         <v>0.43</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5850000000000001</v>
+        <v>0.585</v>
       </c>
       <c r="N12" t="n">
         <v>19.22625000000002</v>
@@ -2026,7 +2026,7 @@
         <v>0.19</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5974999999999999</v>
+        <v>0.5975</v>
       </c>
       <c r="N13" t="n">
         <v>19.84125000000002</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3593</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>196</v>
+      </c>
+      <c r="D75" t="n">
+        <v>210</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-43</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-21.83%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-46</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-46</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.5299999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-4.529999999999982</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.05000000000000004</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3349753694581281</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.586206896551724</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-10.99</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-2.591981132075472</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
